--- a/eval_cases/多轮意图测试用例副本.xlsx
+++ b/eval_cases/多轮意图测试用例副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="23850" windowHeight="12750"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="9" r:id="rId1"/>
